--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,10 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,12 +168,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,19 +781,19 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>321.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F4" s="10" t="n">
+      <c r="E4" s="13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F4" s="13" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>81.7</v>
+      <c r="G4" s="13" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>5.6</v>
@@ -811,25 +802,25 @@
         <v>1564.4</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n">
@@ -839,25 +830,25 @@
         <v>1.4</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
+        <v>62.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>28.9</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -873,22 +864,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F5" s="10" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>15.4</v>
+      <c r="G5" s="3" t="n">
+        <v>5.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -899,13 +890,13 @@
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
@@ -927,8 +918,8 @@
       <c r="U5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="8" t="n">
-        <v>19.5</v>
+      <c r="V5" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.2</v>
@@ -940,7 +931,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,18 +947,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>309.1</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -976,47 +967,47 @@
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.1</v>
+      <c r="J6" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>11</v>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>13.1</v>
+        <v>1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>14.7</v>
+      <c r="R6" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>15.3</v>
+        <v>0.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>1.1</v>
@@ -1041,19 +1032,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>9</v>
+        <v>225.9</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>444.9</v>
@@ -1071,29 +1062,29 @@
       <c r="M7" s="3" t="n">
         <v>34.1</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>15</v>
+      <c r="N7" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>19.3</v>
+        <v>0.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>919</v>
+        <v>100</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>49.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
@@ -1102,13 +1093,13 @@
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1124,22 +1115,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="10" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E8" s="13" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>18.4</v>
+      <c r="F8" s="13" t="n">
+        <v>23.4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>1.2</v>
@@ -1148,7 +1139,7 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>4</v>
@@ -1156,17 +1147,17 @@
       <c r="M8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
+      <c r="N8" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>71.40000000000001</v>
+      <c r="Q8" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>84.5</v>
@@ -1181,12 +1172,12 @@
         <v>6</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1209,26 +1200,29 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>124.9</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>128.9</v>
+        <v>289.5</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>55</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>91.90000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>13.3</v>
+        <v>9</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1350 0
+</t>
+        </is>
       </c>
       <c r="K9" s="3" t="n">
         <v>7.7</v>
@@ -1240,13 +1234,13 @@
         <v>554.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>5</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>48421.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>10.1</v>
@@ -1255,28 +1249,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>914.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.8</v>
+        <v>109.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1297,15 +1291,15 @@
       <c r="D10" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>18.4</v>
+      <c r="E10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148 1
+          <t xml:space="preserve">19 0
 </t>
         </is>
       </c>
@@ -1318,7 +1312,7 @@
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>11</v>
@@ -1333,25 +1327,25 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.1</v>
+        <v>6</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>18.2</v>
@@ -1376,46 +1370,46 @@
       <c r="C11" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13</v>
+      <c r="D11" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>266.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.2</v>
@@ -1424,7 +1418,7 @@
         <v>427.7</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>19.9</v>
+        <v>209.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>22.1</v>
@@ -1432,11 +1426,11 @@
       <c r="W11" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>17.6</v>
+      <c r="X11" s="3" t="n">
+        <v>7.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1457,35 +1451,35 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>18.4</v>
+      <c r="E12" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15.9</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="n">
-        <v>11.7</v>
+      <c r="L12" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>41.1</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1495,29 +1489,29 @@
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>14.7</v>
+      <c r="W12" s="8" t="n">
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>2.2</v>
@@ -1536,25 +1530,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>357.9</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>25.35</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="F13" s="9" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>44.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
@@ -1563,47 +1557,47 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>191.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>18.9</v>
+        <v>180.9</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="S13" s="3" t="n">
+        <v>8.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n">
-        <v>17.7</v>
+      <c r="W13" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1619,28 +1613,28 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G14" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>4.3</v>
@@ -1648,34 +1642,37 @@
       <c r="L14" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>14.8</v>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">048 0
+</t>
+        </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>14.9</v>
+        <v>4</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>56.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n">
-        <v>16.2</v>
+        <v>0.2</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>61</v>
@@ -1684,7 +1681,7 @@
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1700,22 +1697,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="E15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>18.5</v>
+      <c r="F15" s="13" t="n">
+        <v>23.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15.8</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>3.8</v>
@@ -1727,49 +1724,49 @@
         <v>2.1</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>11.3</v>
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>434.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>51.7</v>
+        <v>7.6</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>5.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1785,48 +1782,50 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9994.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="10" t="n">
         <v>56.8</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="13" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>71.2</v>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>139.8</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>59.9</v>
+        <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>58.2</v>
+        <v>8</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>489</v>
+        <v>689</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1191.8</v>
+        <v>110</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>82.2</v>
+        <v>8</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>77.3</v>
@@ -1835,19 +1834,19 @@
         <v>42</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>98.2</v>
+        <v>25</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.1</v>
+        <v>80</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>33.4</v>
@@ -1868,24 +1867,24 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E17" s="10" t="n">
+      <c r="D17" s="13" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E17" s="13" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>18.5</v>
+      <c r="F17" s="13" t="n">
+        <v>18.8</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="H17" s="3" t="n"/>
-      <c r="I17" s="8" t="n">
-        <v>29.4</v>
+      <c r="I17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>44.8</v>
+        <v>4.9</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.1</v>
@@ -1894,46 +1893,46 @@
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>41.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>971.8</v>
+        <v>1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>151.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>46.2</v>
+        <v>6</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>84.7</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>16.1</v>
+      <c r="V17" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1949,23 +1948,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>18.14</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>29.4</v>
+        <v>20.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1976,42 +1975,42 @@
       <c r="L18" s="3" t="n">
         <v>102.2</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>56.5</v>
+      <c r="M18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q18" s="8" t="n">
+        <v>95.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>15.4</v>
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>5.9</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>5.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>10.4</v>
@@ -2030,22 +2029,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E19" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>40.9</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>17.4</v>
+      <c r="F19" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.3</v>
@@ -2057,34 +2056,34 @@
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
+        <v>1.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>64.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>48.5</v>
+        <v>98.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.2</v>
+        <v>0.7</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
@@ -2115,25 +2114,25 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F20" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>4.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.9</v>
@@ -2143,7 +2142,7 @@
         <v>0.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>2</v>
@@ -2152,37 +2151,37 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>51.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>40.5</v>
+        <v>20.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>221.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2198,19 +2197,19 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>12.13</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>2.1</v>
@@ -2231,13 +2230,13 @@
         <v>0.3</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
@@ -2247,13 +2246,13 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>48.2</v>
@@ -2262,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2284,69 +2283,69 @@
         <v>429</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="12" t="n">
-        <v>81.7</v>
+        <v>29.8</v>
+      </c>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="N22" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>14.9</v>
+        <v>9.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="U22" s="3" t="n">
-        <v>15.8</v>
+      <c r="U22" s="8" t="n">
+        <v>59.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>13.9</v>
+      <c r="W22" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>3.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>0.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2362,19 +2361,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="E23" s="16" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>945.4</v>
+      <c r="E23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2399,14 +2398,14 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>18</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>2357.1</v>
@@ -2424,10 +2423,10 @@
         <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>341.5</v>
+        <v>39.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2443,19 +2442,19 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="D24" s="16" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="9" t="n">
         <v>56.1</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>81.90000000000001</v>
+      <c r="F24" s="10" t="n">
+        <v>18.9</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
@@ -2464,21 +2463,23 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2487,25 +2488,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="U24" s="8" t="n">
-        <v>177.4</v>
+      <c r="U24" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>17.2</v>
+        <v>17</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68</v>
       </c>
       <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
@@ -2522,12 +2523,12 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>488.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E25" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="F25" s="3" t="n">
@@ -2542,29 +2543,29 @@
       <c r="I25" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>14.9</v>
+      <c r="J25" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>926</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>24.7</v>
+        <v>29.7</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>1.2</v>
@@ -2573,10 +2574,10 @@
         <v>13.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>469.5</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>24.3</v>
@@ -2589,7 +2590,7 @@
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2605,12 +2606,12 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>34.9</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="F26" s="3" t="n">
@@ -2619,54 +2620,54 @@
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>1.6</v>
+      <c r="H26" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.7</v>
+        <v>5.2</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>63.5</v>
+        <v>3.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>12.2</v>
+        <v>60.9</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>5</v>
@@ -2690,20 +2691,20 @@
       <c r="C27" s="3" t="n">
         <v>390.2</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2712,7 +2713,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>7.2</v>
@@ -2721,40 +2722,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>980.8</v>
-      </c>
       <c r="P27" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>17.6</v>
+        <v>7</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="U27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>123</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2773,70 +2774,70 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>513.3</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F28" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>44.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>22.9</v>
+      <c r="Q28" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>16.7</v>
+        <v>10.9</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>91</v>
@@ -2858,44 +2859,44 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>593.3</v>
+        <v>503.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F29" s="12" t="n">
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>81.2</v>
+      <c r="G29" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>790.9</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
@@ -2904,26 +2905,26 @@
         <v>18.1</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>16.7</v>
+        <v>15</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2939,53 +2940,53 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="E30" s="16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>79.09999999999999</v>
+      <c r="E30" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>900.7</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>29.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>109.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>57.2</v>
+        <v>0.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.9</v>
+        <v>5.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>10</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>0.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>34484.5</v>
@@ -2994,10 +2995,10 @@
         <v>551.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>99.5</v>
+        <v>9.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
@@ -3006,7 +3007,7 @@
         <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3022,16 +3023,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>10.9</v>
+        <v>0</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>15.8</v>
@@ -3043,11 +3044,11 @@
         <v>1.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n">
-        <v>11.9</v>
+        <v>16</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
@@ -3059,31 +3060,31 @@
         <v>4516.1</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>41.6</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>179.3</v>
+      <c r="R31" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>73</v>
@@ -3105,18 +3106,18 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3126,51 +3127,53 @@
         <v>1.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>11.9</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>9</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>116.9</v>
+        <v>6009</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.5</v>
+        <v>0.5</v>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X32" s="3" t="n"/>
+        <v>6.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>71.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3191,44 +3194,44 @@
       <c r="D33" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>19.9</v>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>29.4</v>
+        <v>0.9</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>4.2</v>
@@ -3237,7 +3240,7 @@
         <v>18.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>62.5</v>
+        <v>0.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>10.3</v>
@@ -3249,13 +3252,13 @@
         <v>17.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3273,47 +3276,47 @@
       <c r="C34" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F34" s="10" t="n">
+      <c r="D34" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>0.9</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.9</v>
+        <v>6</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0.2</v>
@@ -3322,25 +3325,25 @@
         <v>18.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>19.6</v>
+      <c r="V34" s="8" t="n">
+        <v>5.9</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3356,15 +3359,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>329.9</v>
+        <v>320.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3380,19 +3383,19 @@
         <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>19.8</v>
+        <v>10</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
@@ -3400,17 +3403,17 @@
       <c r="Q35" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>18.9</v>
+      <c r="R35" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>18.7</v>
@@ -3418,14 +3421,14 @@
       <c r="W35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X35" s="8" t="n">
-        <v>81</v>
+      <c r="X35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3441,19 +3444,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>506.7</v>
+        <v>50.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>14.7</v>
+        <v>19.7</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>9.5</v>
@@ -3467,50 +3470,50 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>12.9</v>
+      <c r="L36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.8</v>
+        <v>10</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>23.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>20.8</v>
+        <v>0.8</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>16.8</v>
+      <c r="X36" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>68.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>212.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3528,14 +3531,14 @@
       <c r="C37" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="10" t="n">
         <v>26.3</v>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>18.3</v>
+      <c r="E37" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>51.1</v>
@@ -3544,54 +3547,54 @@
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>14.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>154.6</v>
+        <v>5</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>34.6</v>
+        <v>39.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3607,15 +3610,15 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D38" s="16" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="E38" s="16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F38" s="12" t="n">
+      <c r="E38" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>99.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3625,55 +3628,55 @@
         <v>46</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>431.7</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>202</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="8" t="n">
         <v>151.5</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>216.4</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>359.5</v>
+        <v>259.5</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3690,19 +3693,19 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4248.1</v>
-      </c>
-      <c r="D39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="F39" s="12" t="n">
+      <c r="E39" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>99.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.9</v>
@@ -3711,10 +3714,10 @@
         <v>2.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>42.1</v>
+        <v>6.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>13</v>
@@ -3723,10 +3726,10 @@
         <v>431.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.6</v>
@@ -3735,31 +3738,31 @@
         <v>151.5</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>10.9</v>
+        <v>216.9</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>16.6</v>
+        <v>10</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>741.9</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3775,44 +3778,44 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="9" t="n">
         <v>42.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>41.8</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 0
+          <t xml:space="preserve">0 00
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.3</v>
@@ -3821,31 +3824,31 @@
         <v>993.6</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>198</v>
+        <v>0</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>212.1</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.9</v>
+        <v>0</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>6.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3861,25 +3864,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>451.2</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>66.5</v>
+      <c r="G41" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.3</v>
@@ -3887,32 +3890,32 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>61.1</v>
+      <c r="L41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N41" s="8" t="n">
-        <v>57.1</v>
+      <c r="N41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>18.4</v>
+        <v>8.5</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>84.5</v>
+        <v>20.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>8</v>
@@ -3920,17 +3923,17 @@
       <c r="V41" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="W41" s="8" t="n">
+      <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3946,76 +3949,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>451.2</v>
+        <v>251.2</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="E42" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>48.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>18.8</v>
+      <c r="N42" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>598</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>16.6</v>
+      <c r="S42" s="8" t="n">
+        <v>60.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>55.9</v>
+        <v>500.9</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>89.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>839</v>
+        <v>89</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.4</v>
+        <v>1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4031,35 +4034,35 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>524.4</v>
+        <v>529.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="9" t="n">
         <v>84.5</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>26</v>
+      <c r="F43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>90.7</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>43.8</v>
@@ -4068,13 +4071,13 @@
         <v>96</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n">
@@ -4084,7 +4087,7 @@
         <v>19.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>163.3</v>
@@ -4108,14 +4111,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>43.4</v>
@@ -4126,11 +4131,11 @@
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>23.1</v>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>0.8</v>
@@ -4143,14 +4148,14 @@
       </c>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
@@ -4171,19 +4176,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16110.9</v>
+        <v>1011</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>109.8</v>
+        <v>10</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>41.8</v>
+        <v>61.8</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>754.6</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>27</v>
@@ -4195,41 +4200,41 @@
         <v>221.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n">
-        <v>22.9</v>
+        <v>200.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.4</v>
+        <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>891.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="n"/>
@@ -4248,39 +4253,39 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>477.8</v>
-      </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>221.9</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>22.9</v>
+        <v>11</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>200.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.7</v>
+        <v>51</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.3</v>
@@ -4289,30 +4294,30 @@
         <v>98.59999999999999</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>54.9</v>
+        <v>0.4</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">110 20
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="n">
-        <v>21.3</v>
+        <v>0.3</v>
       </c>
       <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -53,6 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -61,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,7 +191,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,74 +808,72 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="D4" s="13" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>18.7</v>
+      <c r="E4" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>182.2</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>1564.4</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>1.9</v>
+        <v>97.3</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="16" t="n">
+        <v>111.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R4" s="16" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>1.4</v>
+      <c r="S4" s="16" t="n">
+        <v>1159.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>62.5</v>
+        <v>1642.3</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>22</v>
+        <v>19.1</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>229.9</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -864,74 +889,66 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>382.9</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>19.2</v>
+        <v>382.4</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>1.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5.9</v>
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>17.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N5" s="8" t="n">
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="16" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n"/>
+        <v>90.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>18.3</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
-        <v>80.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -947,73 +964,67 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>6</v>
+        <v>0.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>511</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>16.5</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="Q6" s="16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R6" s="16" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
       <c r="X6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.9</v>
@@ -1032,74 +1043,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>225.9</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.9</v>
+        <v>1275.8</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>17.1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>444.9</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
+        <v>11.9</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" s="16" t="n">
         <v>13.2</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35</v>
+        <v>4.4</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>95</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9</v>
+        <v>99.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3</v>
+        <v>413.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>8.4</v>
+        <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,67 +1126,63 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>23.4</v>
+        <v>391.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.2</v>
+        <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.8</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>20.7</v>
+        <v>1</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>198</v>
+      </c>
+      <c r="P8" s="16" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
+        <v>211.4</v>
+      </c>
+      <c r="R8" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>1176</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1200,77 +1207,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>110.6</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1350 0
-</t>
-        </is>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>554.2</v>
+        <v>521.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>48421.2</v>
+        <v>16485.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.6</v>
+        <v>202.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.1</v>
+        <v>11011.9</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>85.3</v>
+        <v>185.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88</v>
+        <v>188.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>380.5</v>
+        <v>293801.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0</v>
+        <v>184.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>0.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>914.5</v>
+        <v>1414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>109.8</v>
+        <v>119.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1286,74 +1292,69 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>849.9</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 0
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>11</v>
+      <c r="J10" s="16" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="16" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>1118</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>96.8</v>
       </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.2</v>
+      <c r="R10" s="16" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S10" s="16" t="n">
+        <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>261.1</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="X10" s="3" t="n">
+      <c r="W10" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="X10" s="16" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>182.9</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1368,73 +1369,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>266.3</v>
+        <v>110.1</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="16" t="n">
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>1.2</v>
+        <v>17.1</v>
+      </c>
+      <c r="S11" s="16" t="n">
+        <v>19.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>427.7</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>209.9</v>
+        <v>420.1</v>
+      </c>
+      <c r="U11" s="16" t="n">
+        <v>19.9</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>22.1</v>
+        <v>2.2</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>7.6</v>
+        <v>17.6</v>
+      </c>
+      <c r="X11" s="16" t="n">
+        <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1449,72 +1440,66 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
+        <v>12306.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>54.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n">
-        <v>10.7</v>
-      </c>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="P12" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>12.9</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.6</v>
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="W12" s="3" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>2</v>
+        <v>520.1</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1530,74 +1515,70 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>307.9</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>38.03</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>44.4</v>
+        <v>357.9</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.9</v>
+        <v>19.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>4.6</v>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <v>1835.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>180.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>8.9</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>8.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>18.1</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20</v>
+        <v>86.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="16" t="n">
+        <v>847.1</v>
+      </c>
+      <c r="X13" s="16" t="n">
+        <v>129.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1613,76 +1594,61 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G14" s="16" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">048 0
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>58</v>
-      </c>
+        <v>29.5</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="16" t="n">
+        <v>888.2</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="16" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>18.6</v>
+      </c>
+      <c r="V14" s="16" t="n">
+        <v>5456.5</v>
+      </c>
+      <c r="W14" s="3" t="inlineStr"/>
       <c r="X14" s="3" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1953</v>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1697,76 +1663,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>5</v>
+        <v>831</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>58</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>21.2</v>
+      </c>
+      <c r="K15" s="16" t="n">
+        <v>521.6</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="n">
-        <v>0.3</v>
+        <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>434.3</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>5.7</v>
+        <v>199</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q15" s="16" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="R15" s="16" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>1151.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>310</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="U15" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>11.6</v>
+      </c>
+      <c r="X15" s="16" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>18.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,74 +1746,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>128</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="13" t="n">
+        <v>2227.1</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>139.8</v>
+        <v>121.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>58.2</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>689</v>
+        <v>1489.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>110</v>
+        <v>11111</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>8</v>
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.3</v>
+        <v>781.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>42</v>
+        <v>340.1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60</v>
+        <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>25</v>
+        <v>920.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>80</v>
+        <v>801.2</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0</v>
+        <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1865,74 +1829,72 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>445.9</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
+        <v>2445.9</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="I17" s="3" t="n">
-        <v>2</v>
+        <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="16" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
+      <c r="M17" s="16" t="n">
+        <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>41.6</v>
+        <v>21.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>1978.9</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>151.5</v>
+      <c r="R17" s="16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>9.6</v>
+        <v>1948.4</v>
+      </c>
+      <c r="V17" s="16" t="n">
+        <v>119.6</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>0</v>
+      <c r="X17" s="16" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0.8</v>
+        <v>168.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1948,72 +1910,56 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455</v>
-      </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>14555.6</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>16</v>
+        <v>14.4</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="16" t="n">
+        <v>156.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>17.9</v>
-      </c>
+        <v>99.8</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="16" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>5.4</v>
+        <v>21</v>
+      </c>
+      <c r="W18" s="16" t="n">
+        <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>1110.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2029,73 +1975,65 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>530</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>531.9</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>12</v>
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>4.9</v>
+        <v>10.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>22.1</v>
+        <v>264.1</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>64.2</v>
+        <v>63.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.7</v>
+        <v>40.5</v>
+      </c>
+      <c r="U19" s="16" t="n">
+        <v>7.6</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X19" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X19" s="16" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>6.6</v>
@@ -2114,75 +2052,65 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>530</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>35.3</v>
+        <v>542.2</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="16" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>15.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="16" t="n">
+        <v>475.4</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>82198</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2</v>
+        <v>11.3</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>51.3</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>221.1</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>14081.3</v>
+      </c>
+      <c r="U20" s="3" t="inlineStr"/>
+      <c r="V20" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="16" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X20" s="16" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2197,74 +2125,62 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>12.13</v>
+        <v>382.4</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>12.7</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n"/>
+      <c r="R21" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>20</v>
+        <v>18.2</v>
+      </c>
+      <c r="X21" s="16" t="n">
+        <v>208</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>734</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2280,72 +2196,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>1.3</v>
+        <v>1929</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>13.3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n">
-        <v>9</v>
+        <v>18.8</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <v>15.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>9.9</v>
+        <v>91.3</v>
+      </c>
+      <c r="P22" s="16" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="Q22" s="16" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R22" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>49.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>59.8</v>
+        <v>7.9</v>
+      </c>
+      <c r="U22" s="16" t="n">
+        <v>1141</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>3.9</v>
+      <c r="W22" s="16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0.5</v>
+        <v>150.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.9</v>
+        <v>13114.1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2361,72 +2277,70 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>23203.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N23" s="3" t="n"/>
+        <v>64.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>2493</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n"/>
+      <c r="R23" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>18</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2357.1</v>
+        <v>233.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>88.5</v>
+        <v>188.5</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>851.5</v>
+        <v>1851.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>39.5</v>
+        <v>1341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2442,73 +2356,75 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>1464.1</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N24" s="16" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3</v>
+        <v>10.9</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="16" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>15</v>
+        <v>45.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.7</v>
+        <v>1247.9</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>177.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>7</v>
+        <v>41.1</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+        <v>68.8</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>832.1</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2523,74 +2439,50 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F25" s="3" t="n">
+        <v>1988.9</v>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="16" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>13.4</v>
-      </c>
+        <v>29.1</v>
+      </c>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>19.8</v>
+        <v>549.3</v>
+      </c>
+      <c r="U25" s="16" t="n">
+        <v>11.5</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W25" s="16" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X25" s="16" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>851.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2606,74 +2498,70 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F26" s="3" t="n">
+        <v>1349.9</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M26" s="16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>0.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>5.2</v>
+      <c r="R26" s="16" t="n">
+        <v>1156.5</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.2</v>
+        <v>19.2</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="X26" s="8" t="n">
-        <v>10</v>
+        <v>21.6</v>
+      </c>
+      <c r="W26" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5</v>
+        <v>552.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.5</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2689,73 +2577,65 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>390.2</v>
+        <v>340.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
+        <v>25.1</v>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="12" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>11.4</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>1922.6</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" s="3" t="n">
         <v>18</v>
       </c>
+      <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>7.9</v>
+        <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>59.5</v>
+        <v>16.1</v>
+      </c>
+      <c r="X27" s="16" t="n">
+        <v>187.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2774,76 +2654,72 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>2513.8</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G28" s="16" t="n">
         <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>18.7</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>20.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="K28" s="3" t="inlineStr"/>
       <c r="L28" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>3</v>
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <v>2113.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>10</v>
+        <v>15.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q28" s="16" t="n">
+        <v>560.9</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.6</v>
+        <v>82.5</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>9</v>
+        <v>12.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>10.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="V28" s="16" t="n">
+        <v>69.5</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>2</v>
+        <v>15.5</v>
+      </c>
+      <c r="X28" s="16" t="n">
+        <v>478.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2859,73 +2735,73 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>503.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E29" s="20" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>13.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.8</v>
+        <v>22.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>1621.4</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>0.9</v>
+      <c r="L29" s="16" t="n">
+        <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N29" s="3" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90</v>
+        <v>96.8</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>0</v>
+      <c r="R29" s="16" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>448</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>1547.8</v>
+      </c>
+      <c r="U29" s="16" t="n">
+        <v>1108.6</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>7.9</v>
+        <v>17.3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2940,74 +2816,72 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>900.7</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>29.1</v>
+        <v>2284.8</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.8</v>
+        <v>13.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>13.5</v>
-      </c>
+        <v>119.3</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
       <c r="L30" s="3" t="n">
-        <v>0.5</v>
+        <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>56.1</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3" t="n"/>
+        <v>1489</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>10</v>
+        <v>1113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.4</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>189.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>34484.5</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>551.4</v>
+        <v>35.9</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>9.5</v>
+        <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>181.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>83.2</v>
+        <v>183.2</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3023,74 +2897,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>1452</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
+        <v>3.9</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>16</v>
+        <v>11.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>0.3</v>
+      <c r="N31" s="16" t="n">
+        <v>13.9</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4516.1</v>
+        <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>22.6</v>
+      </c>
+      <c r="R31" s="16" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>11</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>10</v>
+      <c r="W31" s="16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>73</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3106,74 +2976,54 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>15.8</v>
-      </c>
+        <v>5208.9</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>11.2</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>6009</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n">
-        <v>21.1</v>
+        <v>29.9</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="16" t="n">
+        <v>2184.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3189,76 +3039,66 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>520</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.9</v>
+        <v>549.1</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17.7</v>
+        <v>0.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="n">
-        <v>5</v>
+        <v>25.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>0</v>
+        <v>198.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>0.5</v>
-      </c>
+        <v>20.9</v>
+      </c>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="inlineStr"/>
       <c r="U33" s="3" t="n">
-        <v>10.3</v>
+        <v>50.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>18</v>
+        <v>18.1</v>
+      </c>
+      <c r="W33" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X33" s="16" t="n">
+        <v>261.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>393.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3274,76 +3114,70 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>18.5</v>
+        <v>1329.1</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.6</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>6</v>
+        <v>1.3</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>16</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>16.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R34" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X34" s="16" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z34" s="3" t="n">
         <v>8</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3359,76 +3193,68 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>320.9</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>15065.7</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0.7</v>
+        <v>51.5</v>
+      </c>
+      <c r="K35" s="16" t="n">
+        <v>80</v>
       </c>
       <c r="L35" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="n">
+      <c r="W35" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="V35" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>16.8</v>
-      </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>10211</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3444,77 +3270,61 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1533.5</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>15.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>9.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>3</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>10.8</v>
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="16" t="n">
+        <v>19.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1591.8</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3529,72 +3339,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>535.5</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>51.1</v>
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>16.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>30.9</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>64.2</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>79.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>9</v>
+        <v>492.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>25.5</v>
+        <v>1859.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8808.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>5</v>
+        <v>316.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20</v>
+        <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>5</v>
+        <v>1838.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3.3</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.6</v>
+        <v>1569.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3610,75 +3420,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>220.9</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>99.7</v>
+        <v>12443.1</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>61.6</v>
+        <v>11.3</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>431.7</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>28.1</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>151.5</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>88</v>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>0</v>
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="16" t="n">
+        <v>18.1</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>89.8</v>
+        <v>20.2</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>259.5</v>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+        <v>11.8</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>1569.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3693,76 +3497,60 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
+        <v>579.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>2.8</v>
+        <v>45.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>431.7</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.1</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R39" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>89.8</v>
+        <v>1720.2</v>
+      </c>
+      <c r="U39" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="V39" s="16" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X39" s="16" t="n">
+        <v>27.5</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
+        <v>26</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3778,77 +3566,72 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>15.9</v>
+        <v>353.1</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>21.4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 00
-</t>
-        </is>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>993.6</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q40" s="16" t="n">
+        <v>522</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.1</v>
+        <v>21.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>169.5</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>12.7</v>
+      </c>
+      <c r="V40" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>6.9</v>
+        <v>18.5</v>
+      </c>
+      <c r="X40" s="16" t="n">
+        <v>98.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>70</v>
+        <v>988</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3864,76 +3647,70 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>251.2</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="8" t="n">
+        <v>1451.2</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>128.13</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="16" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="N41" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="O41" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>8.5</v>
+        <v>1198</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>216.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
+        <v>2943.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>10.7</v>
+        <v>19.9</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0</v>
+        <v>6.1</v>
+      </c>
+      <c r="X41" s="16" t="n">
+        <v>148.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>31.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3949,77 +3726,63 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>251.2</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.8</v>
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>25.3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>2</v>
+        <v>26.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>500.9</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
       <c r="U42" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4033,70 +3796,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="X43" s="3" t="n"/>
-      <c r="Y43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="20" t="inlineStr"/>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4110,58 +3833,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>35.1</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4176,69 +3871,73 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>754.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>27</v>
-      </c>
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>10291.7</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>1641.8</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>114.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>221.9</v>
+        <v>121.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n"/>
+        <v>1080</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>200.9</v>
+        <v>444.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>0</v>
+        <v>9571.799999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0</v>
+        <v>1661</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>891.9</v>
+        <v>271.3</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4253,72 +3952,65 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="10" t="n">
+        <v>19477.2</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>221.9</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>200.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>51</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I46" s="16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="N46" s="16" t="n">
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>16.5</v>
+        <v>47.4</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>1116.1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110 20
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>54.9</v>
+      </c>
+      <c r="U46" s="16" t="n">
+        <v>1941.4</v>
+      </c>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,30 +146,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -189,6 +159,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -808,66 +787,70 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>391.2</v>
+        <v>3012.1</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>182.2</v>
+        <v>18.5</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="16" t="n">
-        <v>111.9</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="16" t="n">
+      <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="16" t="n">
-        <v>1159.9</v>
+      <c r="S4" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1642.3</v>
+        <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="16" t="n">
-        <v>229.9</v>
+      <c r="V4" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
@@ -894,17 +877,17 @@
       <c r="D5" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>1.1</v>
+      <c r="E5" s="11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>19.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>15.4</v>
+        <v>15.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -913,42 +896,52 @@
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.6</v>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="16" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Y5" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.5</v>
+        <v>66.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -967,10 +960,10 @@
         <v>309.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>18.4</v>
@@ -979,52 +972,58 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" s="16" t="n">
-        <v>511</v>
-      </c>
-      <c r="N6" s="16" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q6" s="16" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="R6" s="16" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="Q6" s="8" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="X6" s="3" t="n">
-        <v>0.7</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.9</v>
@@ -1043,74 +1042,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1275.8</v>
+        <v>275.8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>21.24</v>
+        <v>21.6</v>
       </c>
       <c r="E7" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.4</v>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N7" s="16" t="n">
-        <v>95</v>
+      <c r="M7" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>413.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>119.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>7.7</v>
+        <v>16.8</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V7" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1126,22 +1127,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
+        <v>291.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>8.1</v>
+        <v>26.8</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>18.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1150,39 +1151,43 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="16" t="n">
-        <v>106.6</v>
+        <v>10.8</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>190.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="P8" s="16" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="R8" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="R8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>1176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="n">
-        <v>7.3</v>
+        <v>6</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>97.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1210,70 +1215,70 @@
         <v>1749.7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>128.9</v>
+        <v>129</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="G9" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>110.6</v>
+        <v>60.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>521.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>16485.8</v>
+        <v>484.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>202.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>11011.9</v>
+        <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.9</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>188.5</v>
+        <v>885.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>293801.5</v>
+        <v>9501.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>184.9</v>
+        <v>8.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>911.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1414.5</v>
+        <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>119.8</v>
@@ -1303,58 +1308,66 @@
       <c r="F10" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>15.8</v>
+      <c r="G10" s="11" t="n">
+        <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>797.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>1118</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>3</v>
+      <c r="M10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>96.8</v>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S10" s="16" t="n">
+      <c r="S10" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="U10" s="3" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="16" t="n">
+      <c r="X10" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="Z10" s="3" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1369,63 +1382,77 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>909.3</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>34.3</v>
+        <v>27.3</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5.7</v>
+        <v>10.7</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>16.9</v>
+      <c r="G11" s="11" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>84.7</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>110.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="16" t="n">
-        <v>26.3</v>
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>66.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="16" t="n">
-        <v>19.4</v>
+      <c r="S11" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>420.1</v>
-      </c>
-      <c r="U11" s="16" t="n">
+        <v>862</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W11" s="3" t="n">
+      <c r="V11" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W11" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="16" t="n">
-        <v>17.6</v>
+      <c r="X11" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1440,29 +1467,35 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>12306.1</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E12" s="11" t="n">
+        <v>506.7</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>13</v>
+      </c>
       <c r="H12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>54.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>19.7</v>
+      </c>
       <c r="M12" s="3" t="n">
         <v>22.1</v>
       </c>
@@ -1470,36 +1503,40 @@
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S12" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="S12" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>20.4</v>
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="X12" s="3" t="n">
-        <v>0.3</v>
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>520.1</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1515,70 +1552,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>357.9</v>
+        <v>3514.9</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25.31</v>
+        <v>25.5</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>14.1</v>
+        <v>18.2</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>14.7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.4</v>
+        <v>11.9</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
+        <v>2.3</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>11.5</v>
+      </c>
       <c r="M13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>1835.6</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>8.9</v>
+      <c r="P13" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>180.9</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S13" s="16" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V13" s="3" t="inlineStr"/>
-      <c r="W13" s="16" t="n">
-        <v>847.1</v>
-      </c>
-      <c r="X13" s="16" t="n">
-        <v>129.1</v>
+        <v>3</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W13" s="8" t="n">
+        <v>6816.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1594,61 +1637,77 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="G14" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>11.3</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="16" t="n">
-        <v>888.2</v>
+        <v>28.3</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="16" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="R14" s="16" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S14" s="16" t="n">
-        <v>156.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U14" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V14" s="16" t="n">
-        <v>5456.5</v>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="n">
-        <v>6</v>
+        <v>8.6</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1953</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+        <v>199</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1663,19 +1722,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>831</v>
+        <v>1638</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>58</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1684,53 +1743,55 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K15" s="16" t="n">
-        <v>521.6</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="n">
-        <v>11.3</v>
+        <v>5.7</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>711.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P15" s="16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="16" t="n">
-        <v>225.5</v>
-      </c>
-      <c r="R15" s="16" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S15" s="16" t="n">
-        <v>1151.7</v>
+        <v>99</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>57.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U15" s="16" t="n">
-        <v>12</v>
+        <v>168</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="X15" s="16" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>18.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1748,14 +1809,14 @@
       <c r="C16" s="3" t="n">
         <v>2227.1</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>132</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>92.5</v>
+      <c r="D16" s="17" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>9.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>71.2</v>
@@ -1764,56 +1825,58 @@
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>121.8</v>
+        <v>51.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>59.1</v>
+        <v>591.7</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>67.90000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>1489.8</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11111</v>
+        <v>17119</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.2</v>
+        <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>781.7</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>340.1</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>920.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.2</v>
+        <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>364</v>
+        <v>2369.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.9</v>
+        <v>393.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1829,72 +1892,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2445.9</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>24.2</v>
+        <v>445.9</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="16" t="n">
+      <c r="M17" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>21.3</v>
+      <c r="N17" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1978.9</v>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
+        <v>97.8</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>7.4</v>
+      </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S17" s="16" t="n">
+      <c r="R17" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>162</v>
+        <v>72.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1948.4</v>
-      </c>
-      <c r="V17" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
         <v>119.6</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="X17" s="16" t="n">
-        <v>16.4</v>
+      <c r="W17" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>168.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1910,56 +1975,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>14555.6</v>
+        <v>455.1</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="16" t="n">
+      <c r="E18" s="15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>1610.5</v>
+      </c>
+      <c r="O18" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="16" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="16" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="16" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>149</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1110.1</v>
+        <v>11.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1975,68 +2060,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.9</v>
+        <v>95311.10000000001</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="n">
+      <c r="E19" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="16" t="n">
-        <v>19</v>
+      <c r="M19" s="8" t="n">
+        <v>111</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>264.1</v>
+        <v>23.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>63.2</v>
+        <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U19" s="16" t="n">
-        <v>7.6</v>
+        <v>94.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X19" s="16" t="n">
+      <c r="W19" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2057,60 +2150,72 @@
       <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="16" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>15.8</v>
+      <c r="E20" s="15" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>475.4</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M20" s="16" t="n">
-        <v>82198</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>11.3</v>
+        <v>5.9</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>811</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
+        <v>98.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="3" t="inlineStr"/>
+      <c r="S20" s="8" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>14081.3</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="16" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="16" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X20" s="16" t="n">
-        <v>219.7</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr"/>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="W20" s="8" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>721</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2130,57 +2235,71 @@
       <c r="D21" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F21" s="3" t="n">
+      <c r="E21" s="11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="H21" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J21" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="n">
-        <v>14.9</v>
+        <v>11.3</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>54.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="16" t="n">
-        <v>208</v>
+      <c r="X21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>734</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2196,72 +2315,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1929</v>
+        <v>194828.8</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>13.3</v>
+        <v>18.6</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M22" s="16" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="N22" s="16" t="n">
-        <v>15.1</v>
+      <c r="M22" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="P22" s="16" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="Q22" s="16" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R22" s="16" t="n">
+        <v>992</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="16" t="n">
+      <c r="S22" s="8" t="n">
         <v>49.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="U22" s="16" t="n">
-        <v>1141</v>
+        <v>49.5</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="16" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="16" t="n">
+      <c r="X22" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>150.5</v>
+        <v>505.9</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>13114.1</v>
+        <v>1199.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2277,70 +2400,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23203.1</v>
+        <v>12320.8</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="22" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="F23" s="22" t="n">
+      <c r="E23" s="17" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F23" s="17" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>73.09999999999999</v>
+      <c r="G23" s="3" t="n">
+        <v>75.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>5.9</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>64.8</v>
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12.6</v>
+        <v>711.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>781.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>233.1</v>
+        <v>2351.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>1851.5</v>
+        <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1341.5</v>
+        <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>141</v>
+        <v>541</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2356,74 +2485,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1464.1</v>
+        <v>484.1</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>191.9</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>65.09999999999999</v>
+        <v>26.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="16" t="n">
-        <v>18.9</v>
+      <c r="N24" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>45.4</v>
+        <v>129.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1247.9</v>
-      </c>
-      <c r="U24" s="16" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="U24" s="8" t="n">
         <v>177.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="X24" s="16" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.8</v>
+        <v>168.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>832.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2439,50 +2570,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1988.9</v>
-      </c>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="16" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="G25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>549.3</v>
-      </c>
-      <c r="U25" s="16" t="n">
-        <v>11.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="16" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X25" s="16" t="n">
-        <v>16.8</v>
+      <c r="W25" s="8" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>116.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>851.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2498,7 +2655,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>24.4</v>
@@ -2513,55 +2670,61 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.3</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M26" s="16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="16" t="n">
-        <v>1156.5</v>
-      </c>
-      <c r="S26" s="16" t="n">
+      <c r="R26" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>6.3</v>
+        <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="16" t="n">
-        <v>15.5</v>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>552.1</v>
+        <v>194</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>211.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2579,66 +2742,74 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="12" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>11.4</v>
+      <c r="D27" s="11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="L27" s="16" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="M27" s="16" t="n">
-        <v>1922.6</v>
+      <c r="L27" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="O27" s="3" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>1618.1</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="T27" s="3" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="X27" s="16" t="n">
-        <v>187.5</v>
+      <c r="X27" s="8" t="n">
+        <v>15859.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>93</v>
+        <v>913</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2654,72 +2825,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2513.8</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>15.9</v>
+        <v>313.3</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>15.1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="I28" s="16" t="n">
-        <v>20.9</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>5.5</v>
+      </c>
       <c r="L28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="16" t="n">
-        <v>2113.3</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q28" s="16" t="n">
-        <v>560.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>82.5</v>
+        <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>12.8</v>
+        <v>19</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V28" s="16" t="n">
-        <v>69.5</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>645.4</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="16" t="n">
-        <v>478.2</v>
+      <c r="X28" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>191</v>
+        <v>1891</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2735,73 +2910,77 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>593.3</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E29" s="20" t="inlineStr"/>
-      <c r="F29" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>13.8</v>
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>1621.4</v>
+        <v>3.8</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="16" t="n">
-        <v>10.9</v>
+      <c r="L29" s="8" t="n">
+        <v>109.7</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.8</v>
+        <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="R29" s="16" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="S29" s="16" t="n">
-        <v>448</v>
+        <v>8.6</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>517.1</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>1547.8</v>
-      </c>
-      <c r="U29" s="16" t="n">
-        <v>1108.6</v>
+        <v>57.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>11.6</v>
+        <v>17.5</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>12.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>111.9</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2816,66 +2995,70 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="22" t="n">
+        <v>22848.3</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="22" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F30" s="22" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="E30" s="11" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G30" s="11" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.8</v>
+        <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
+        <v>119.5</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>113.5</v>
+      </c>
       <c r="L30" s="3" t="n">
-        <v>57.2</v>
+        <v>51.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="N30" s="3" t="inlineStr"/>
+        <v>56.7</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>1489</v>
+        <v>9489</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>1113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>851.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>189.9</v>
+        <v>844.7</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>365</v>
@@ -2897,70 +3080,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1452</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E31" s="22" t="n">
+        <v>1532</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="G31" s="16" t="n">
+      <c r="F31" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G31" s="8" t="n">
         <v>58.4</v>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>11.9</v>
+        <v>39.1</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N31" s="16" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>412.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="16" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="S31" s="16" t="n">
+      <c r="R31" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="U31" s="3" t="inlineStr"/>
+        <v>13.1</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>211.1</v>
+      </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="16" t="n">
+      <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2976,54 +3165,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5208.9</v>
+        <v>528</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>17.7</v>
+      </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>10.1</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q32" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R32" s="16" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S32" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="16" t="n">
-        <v>2184.9</v>
+      <c r="T32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="3" t="inlineStr"/>
+      <c r="X32" s="8" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3039,66 +3250,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>549.1</v>
+        <v>349.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>0.4</v>
+      <c r="G33" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>25.4</v>
+        <v>2.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.1</v>
+        <v>6.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>18.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>198.8</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="16" t="n">
+      <c r="Q33" s="8" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="T33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="U33" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W33" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X33" s="16" t="n">
-        <v>261.1</v>
+        <v>5</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>393.8</v>
+        <v>16</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3114,70 +3335,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1329.1</v>
+        <v>329.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H34" s="16" t="n">
         <v>19.1</v>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="G34" s="11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>21.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="16" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S34" s="16" t="n">
-        <v>81.7</v>
+      <c r="R34" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72.8</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X34" s="16" t="n">
-        <v>116.8</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="W34" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>81</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.8</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3193,7 +3420,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>15065.7</v>
+        <v>5056.7</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>26.8</v>
@@ -3204,57 +3431,65 @@
       <c r="F35" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="G35" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="J35" s="3" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="K35" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="L35" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>84.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>49</v>
+        <v>1891</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R35" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="S35" s="3" t="n">
-        <v>19.6</v>
+        <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>22.5</v>
+        <v>252</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>168.5</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>10211</v>
+        <v>8</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3270,22 +3505,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1533.5</v>
+        <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.9</v>
@@ -3293,17 +3528,23 @@
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>12.6</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
@@ -3311,19 +3552,27 @@
       <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="16" t="n">
-        <v>19.8</v>
+      <c r="S36" s="8" t="n">
+        <v>65.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1591.8</v>
-      </c>
-      <c r="U36" s="16" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3339,72 +3588,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>2290.9</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>128.5</v>
+        <v>129.5</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>62.3</v>
+        <v>61.9</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>16.3</v>
+        <v>95.7</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>65.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>167.9</v>
+      </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>79.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492.9</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1859.9</v>
+        <v>115.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>811.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8808.9</v>
+        <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>316.9</v>
+        <v>116.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>4.4</v>
+        <v>554.5</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>1838.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1569.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3420,7 +3673,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>12443.1</v>
+        <v>448.9</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>25.6</v>
@@ -3431,8 +3684,8 @@
       <c r="F38" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>11.3</v>
+      <c r="G38" s="11" t="n">
+        <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3440,48 +3693,54 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="16" t="n">
+      <c r="J38" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="M38" s="16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="P38" s="3" t="inlineStr"/>
+        <v>984.9</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>217.6</v>
+      </c>
       <c r="T38" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="U38" s="16" t="n">
-        <v>18.1</v>
+        <v>83.5</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="16" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X38" s="16" t="n">
+      <c r="W38" s="8" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>1569.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3497,60 +3756,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>579.9</v>
-      </c>
-      <c r="D39" s="3" t="n">
+        <v>5372.9</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E39" s="20" t="inlineStr"/>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="16" t="n">
-        <v>15.1</v>
+      <c r="G39" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>45.3</v>
+        <v>6.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
-      <c r="P39" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="16" t="n">
-        <v>80</v>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
+      <c r="R39" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="T39" s="3" t="n">
-        <v>1720.2</v>
-      </c>
-      <c r="U39" s="16" t="n">
+        <v>58146.9</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="V39" s="16" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W39" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X39" s="16" t="n">
-        <v>27.5</v>
+      <c r="V39" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>11.5</v>
+        <v>141.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3566,69 +3839,71 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>353.1</v>
+        <v>52.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>22.2</v>
+        <v>27.6</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>14.44</v>
+        <v>10.2</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G40" s="16" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>7.3</v>
+        <v>18.9</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q40" s="16" t="n">
-        <v>522</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>21.8</v>
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>169.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="V40" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X40" s="16" t="n">
-        <v>98.3</v>
+      <c r="W40" s="8" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>988</v>
+        <v>83</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3647,70 +3922,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1451.2</v>
+        <v>458.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.4</v>
+        <v>12.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>128.13</v>
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="8" t="n">
+        <v>51.9</v>
+      </c>
       <c r="I41" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="16" t="n">
-        <v>88.3</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>88.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="16" t="n">
-        <v>11</v>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1198</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="16" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="S41" s="16" t="n">
-        <v>216.6</v>
+      <c r="R41" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2943.5</v>
+        <v>4213.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V41" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="X41" s="16" t="n">
-        <v>148.2</v>
+        <v>15.5</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>31.9</v>
+        <v>1112</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3726,7 +4007,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>524.4</v>
+        <v>5254.4</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>27.2</v>
@@ -3737,30 +4018,32 @@
       <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>25.3</v>
+      <c r="G42" s="15" t="n">
+        <v>15.2</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
+        <v>15.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="n">
-        <v>1.3</v>
+      <c r="M42" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.8</v>
@@ -3768,19 +4051,27 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S42" s="16" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
+      <c r="R42" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>153.2</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -3796,10 +4087,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="20" t="inlineStr"/>
-      <c r="E43" s="20" t="inlineStr"/>
-      <c r="F43" s="20" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3833,10 +4126,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="20" t="inlineStr"/>
-      <c r="E44" s="20" t="inlineStr"/>
-      <c r="F44" s="20" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3873,42 +4168,44 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="22" t="n">
-        <v>10291.7</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>1641.8</v>
-      </c>
-      <c r="F45" s="22" t="n">
+      <c r="D45" s="17" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>114.4</v>
+        <v>119.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>121.3</v>
+        <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.2</v>
+        <v>49</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>444.9</v>
+        <v>212.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>9571.799999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.3</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -3917,26 +4214,26 @@
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1661</v>
+        <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>271.3</v>
+        <v>851.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>67.3</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
+      <c r="Y45" s="3" t="n">
+        <v>1263</v>
+      </c>
       <c r="Z45" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>331.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3952,10 +4249,10 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>19477.2</v>
+        <v>5417.8</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>10.4</v>
@@ -3963,54 +4260,62 @@
       <c r="F46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>16.9</v>
+      <c r="G46" s="8" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="H46" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>654.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>1860.8</v>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="I46" s="16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="16" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="N46" s="16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="S46" s="16" t="n">
-        <v>1116.1</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="U46" s="16" t="n">
-        <v>1941.4</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,16 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -787,7 +778,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3012.1</v>
+        <v>301.2</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>27.8</v>
@@ -802,7 +793,7 @@
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -823,24 +814,24 @@
         <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>19.1</v>
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -856,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -883,8 +874,8 @@
       <c r="F5" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>15.9</v>
+      <c r="G5" s="8" t="n">
+        <v>59.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>7.9</v>
@@ -898,11 +889,11 @@
       <c r="K5" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>29.5</v>
+      <c r="L5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>19.4</v>
+        <v>8149.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -911,13 +902,13 @@
         <v>90</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="R5" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
@@ -925,14 +916,12 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="8" t="n">
-        <v>199.5</v>
+        <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>19.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -941,7 +930,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>66.5</v>
+        <v>469.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -972,7 +961,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -981,13 +970,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>69.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>211</v>
+        <v>1.1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
@@ -999,10 +988,10 @@
         <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>11.6</v>
@@ -1011,22 +1000,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>18.3</v>
+        <v>24.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1045,25 +1034,25 @@
         <v>275.8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>112.9</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1078,27 +1067,27 @@
         <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>77.5</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1111,7 +1100,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1127,16 +1116,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
+        <v>391.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
@@ -1151,27 +1140,27 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>190.6</v>
+      <c r="M8" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R8" s="8" t="n">
+        <v>2719.4</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1186,8 +1175,8 @@
       <c r="V8" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1212,31 +1201,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>43927.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>129</v>
+        <v>128.9</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>55</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>60.6</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>56.7</v>
@@ -1245,10 +1234,10 @@
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>25.1</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484.8</v>
+        <v>684.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.6</v>
@@ -1260,28 +1249,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>885.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9501.5</v>
+        <v>3801.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>911.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>119.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1286,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>849.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>25.8</v>
@@ -1318,11 +1307,9 @@
         <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>797.4</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>418.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
@@ -1336,7 +1323,7 @@
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1348,10 +1335,10 @@
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>7.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
@@ -1366,7 +1353,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1382,25 +1369,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>909.3</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="13" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>84.7</v>
+      <c r="I11" s="3" t="n">
+        <v>4.7</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
@@ -1409,43 +1396,43 @@
         <v>0.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>66.5</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>862</v>
+        <v>512</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
@@ -1467,10 +1454,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>29.9</v>
+        <v>506.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>5.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
@@ -1478,38 +1465,38 @@
       <c r="F12" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>13</v>
+      <c r="G12" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>15.5</v>
@@ -1520,23 +1507,23 @@
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>4.6</v>
+      <c r="U12" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1552,10 +1539,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3514.9</v>
+        <v>357.9</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>11.3</v>
@@ -1564,37 +1551,37 @@
         <v>18.2</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="P13" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>180.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>17.3</v>
@@ -1603,7 +1590,7 @@
         <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1612,16 +1599,16 @@
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>6816.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>791.5</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1637,40 +1624,40 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+      <c r="L14" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1678,23 +1665,21 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q14" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>19.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>6.2</v>
@@ -1703,10 +1688,10 @@
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>28.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1722,7 +1707,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1638</v>
+        <v>631</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>26</v>
@@ -1748,14 +1733,14 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>711.3</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1767,25 +1752,25 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>57.9</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>15.8</v>
+        <v>48</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>69.40000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
@@ -1809,16 +1794,16 @@
       <c r="C16" s="3" t="n">
         <v>2227.1</v>
       </c>
-      <c r="D16" s="17" t="n">
-        <v>1298</v>
-      </c>
-      <c r="E16" s="17" t="n">
+      <c r="D16" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>56.8</v>
       </c>
-      <c r="F16" s="17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1828,43 +1813,43 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>51.8</v>
+        <v>21.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>591.7</v>
+        <v>5.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>17119</v>
+        <v>1111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310.9</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>160.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>801.7</v>
@@ -1873,10 +1858,10 @@
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2369.8</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>393.9</v>
+        <v>33.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1894,26 +1879,26 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="17" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>5.8</v>
+      <c r="J17" s="8" t="n">
+        <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
@@ -1929,7 +1914,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1937,20 +1922,20 @@
       <c r="R17" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>72.2</v>
+        <v>42</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>119.6</v>
+      <c r="V17" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
         <v>16.5</v>
@@ -1975,40 +1960,40 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.1</v>
+        <v>455.5</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G18" s="15" t="n">
+      <c r="E18" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>61.5</v>
+        <v>1666.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>1610.5</v>
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>19</v>
@@ -2020,31 +2005,31 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>101.4</v>
+        <v>110.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>11.6</v>
+        <v>110.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2060,7 +2045,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>95311.10000000001</v>
+        <v>531.9</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>28</v>
@@ -2078,19 +2063,19 @@
         <v>7.2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>11.2</v>
+        <v>111.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>13</v>
@@ -2098,11 +2083,11 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>0.4</v>
+      <c r="P19" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18</v>
@@ -2111,7 +2096,7 @@
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>94.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>7.2</v>
@@ -2119,10 +2104,10 @@
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2150,13 +2135,13 @@
       <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="15" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2166,22 +2151,22 @@
         <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>111.2</v>
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>811</v>
+        <v>211</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98.2</v>
+        <v>198</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2192,7 +2177,7 @@
       <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
@@ -2205,13 +2190,13 @@
         <v>22.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>29.9</v>
+        <v>299.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>721</v>
+        <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.6</v>
@@ -2233,25 +2218,25 @@
         <v>382.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2263,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>54.9</v>
+        <v>15.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2281,7 +2266,7 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
@@ -2299,7 +2284,7 @@
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2315,31 +2300,31 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>194828.8</v>
+        <v>9489</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>82.8</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
@@ -2348,22 +2333,22 @@
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>992</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>49.5</v>
@@ -2378,13 +2363,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>13.8</v>
+        <v>53.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>505.9</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1199.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2400,19 +2385,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.8</v>
+        <v>12320.3</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="F23" s="17" t="n">
+      <c r="E23" s="11" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.7</v>
+      <c r="G23" s="11" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2424,7 +2409,7 @@
         <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>2.5</v>
@@ -2433,7 +2418,7 @@
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>711.5</v>
+        <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>293</v>
@@ -2445,13 +2430,13 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>781.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2351.7</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>88.5</v>
@@ -2469,7 +2454,7 @@
         <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>541</v>
+        <v>41</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2485,7 +2470,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>484.1</v>
+        <v>2464.1</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>26.5</v>
@@ -2496,35 +2481,33 @@
       <c r="F24" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>15.1</v>
+      <c r="G24" s="8" t="n">
+        <v>57.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>29.4</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2533,25 +2516,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>129.6</v>
+        <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>177.7</v>
+        <v>177.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2570,40 +2553,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>428.9</v>
+        <v>1488.9</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>25.9</v>
+        <v>32.7</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>16</v>
+      <c r="G25" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>15.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>49.7</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>5.4</v>
+        <v>19.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>18</v>
@@ -2611,35 +2594,35 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
+      <c r="Q25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>37.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>13.8</v>
+        <v>113.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>116.8</v>
+        <v>216.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2670,40 +2653,40 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>19.4</v>
+        <v>109.4</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="R26" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
@@ -2715,16 +2698,16 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>211.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2743,19 +2726,19 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>24.5</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>14</v>
+      <c r="G27" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2764,7 +2747,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="L27" s="8" t="n">
         <v>12.4</v>
@@ -2773,40 +2756,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>1618.1</v>
+        <v>1618.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>15859.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>913</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2825,51 +2808,51 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>313.3</v>
+        <v>513.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>15.1</v>
+      <c r="G28" s="13" t="n">
+        <v>15.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>935.4</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>12.1</v>
+      <c r="N28" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2881,17 +2864,17 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="8" t="n">
-        <v>645.4</v>
+      <c r="V28" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>11</v>
+        <v>817</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>1891</v>
+        <v>191</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>11.8</v>
@@ -2910,7 +2893,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>323.3</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>28.3</v>
@@ -2930,38 +2913,38 @@
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="8" t="n">
-        <v>25.2</v>
+      <c r="J29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>109.7</v>
+        <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>517.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2970,16 +2953,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>12.7</v>
+        <v>17.3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2995,7 +2978,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.3</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>131.2</v>
@@ -3010,7 +2993,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
@@ -3022,34 +3005,32 @@
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>51.2</v>
+        <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>9489</v>
+        <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1113.2</v>
+        <v>113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>851.7</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>844.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3080,7 +3061,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1532</v>
+        <v>432</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>26.2</v>
@@ -3095,7 +3076,7 @@
         <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
@@ -3103,50 +3084,48 @@
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>412.8</v>
+        <v>11.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="V31" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
-        <v>16.4</v>
+      <c r="W31" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3165,28 +3144,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>528</v>
+        <v>5280.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G32" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G32" s="11" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -3195,33 +3174,33 @@
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3231,10 +3210,10 @@
         <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3253,25 +3232,25 @@
         <v>349.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>11.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>11.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>95.90000000000001</v>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>6.8</v>
@@ -3280,46 +3259,46 @@
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.6</v>
+        <v>11.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>203.5</v>
+      <c r="Q33" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3338,40 +3317,40 @@
         <v>329.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>19.7</v>
+      <c r="H34" s="8" t="n">
+        <v>49.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>71.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>18.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3379,8 +3358,8 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="R34" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>18.7</v>
@@ -3389,22 +3368,22 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>81</v>
+      <c r="X34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3420,7 +3399,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5056.7</v>
+        <v>506.7</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>26.8</v>
@@ -3441,7 +3420,7 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>21.1</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3452,17 +3431,17 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>84.8</v>
+      <c r="N35" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1891</v>
+        <v>189</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>38.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>17.6</v>
@@ -3471,7 +3450,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="U35" s="8" t="n">
         <v>12.8</v>
@@ -3480,13 +3459,13 @@
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>67.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>168.5</v>
+        <v>683.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3508,13 +3487,13 @@
         <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>10.7</v>
+        <v>10.54</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>15.9</v>
@@ -3537,11 +3516,11 @@
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>12.6</v>
+      <c r="N36" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.1</v>
@@ -3552,11 +3531,11 @@
       <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>65.8</v>
+      <c r="S36" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="U36" s="8" t="n">
         <v>17.9</v>
@@ -3564,14 +3543,14 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="8" t="n">
-        <v>14.6</v>
+      <c r="W36" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3588,25 +3567,25 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2290.9</v>
+        <v>2140.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>129.5</v>
+        <v>128.5</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>61.9</v>
+        <v>60.9</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>65.7</v>
+        <v>94.7</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>67.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>167.9</v>
+        <v>141.7</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
@@ -3615,49 +3594,49 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>64.5</v>
+        <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.9</v>
+        <v>185.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>811.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>116.9</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>554.5</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>89.8</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>3.9</v>
+        <v>39.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3673,13 +3652,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.9</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>18.9</v>
@@ -3693,24 +3672,24 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>20.1</v>
+      <c r="J38" s="3" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>2.8</v>
+        <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>984.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
@@ -3719,25 +3698,25 @@
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>217.6</v>
+        <v>127.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>83.5</v>
+        <v>23.3</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3756,10 +3735,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5372.9</v>
+        <v>579.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>10.9</v>
@@ -3767,12 +3746,12 @@
       <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>12.9</v>
+      <c r="G39" s="11" t="n">
+        <v>15.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3784,16 +3763,16 @@
         <v>12.7</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
@@ -3802,10 +3781,10 @@
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58146.9</v>
+        <v>92.5</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>18</v>
@@ -3814,7 +3793,7 @@
         <v>12.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>157.5</v>
+        <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>12.3</v>
@@ -3823,7 +3802,7 @@
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>141.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3839,25 +3818,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>52.5</v>
+        <v>35.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>21.4</v>
+        <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
@@ -3876,19 +3855,19 @@
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3897,16 +3876,16 @@
         <v>12.7</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>181.3</v>
+        <v>181.5</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3922,13 +3901,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.6</v>
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>8.6</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>18.5</v>
@@ -3936,11 +3915,9 @@
       <c r="G41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51.9</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
@@ -3949,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
@@ -3967,13 +3944,13 @@
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S41" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>4213.5</v>
+        <v>423.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3982,16 +3959,16 @@
         <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1112</v>
+        <v>19.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4007,7 +3984,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5254.4</v>
+        <v>529.4</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>27.2</v>
@@ -4018,14 +3995,14 @@
       <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="15" t="n">
-        <v>15.2</v>
+      <c r="G42" s="13" t="n">
+        <v>135.2</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>15.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -4033,13 +4010,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4052,24 +4029,24 @@
         <v>26.6</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>148.7</v>
+        <v>12.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>153.2</v>
+        <v>43.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
+      <c r="V42" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4168,23 +4145,23 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="17" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>41.8</v>
+      <c r="D45" s="14" t="n">
+        <v>1091.7</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>61.8</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.9</v>
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.4</v>
+        <v>119.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
@@ -4193,19 +4170,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>212.9</v>
+        <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4220,20 +4197,22 @@
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>831.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>67.5</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>200.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
         <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.9</v>
+        <v>2331.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4249,7 +4228,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5417.8</v>
+        <v>417.8</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>27.3</v>
@@ -4269,15 +4248,15 @@
       <c r="I46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>52.4</v>
+      <c r="J46" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>41.1</v>
+        <v>11181.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4289,29 +4268,29 @@
         <v>6.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>24.7</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>654.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
-      </c>
+        <v>54.1</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Y46" s="3" t="n">
-        <v>1860.8</v>
+        <v>1862.4</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -892,8 +892,8 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>8149.4</v>
+      <c r="M5" s="13" t="n">
+        <v>814.9399999999999</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -972,7 +972,7 @@
       <c r="K6" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="13" t="n">
         <v>1.1</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -1157,8 +1157,8 @@
       <c r="P8" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>2719.4</v>
+      <c r="Q8" s="13" t="n">
+        <v>271.94</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.9</v>
@@ -1224,13 +1224,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="14" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="14" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1242,10 +1242,10 @@
       <c r="P9" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="14" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="14" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1257,10 +1257,10 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="14" t="n">
         <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1310,10 +1310,10 @@
         <v>418.1</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="14" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="14" t="n">
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -1325,10 +1325,10 @@
       <c r="P10" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="14" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="14" t="n">
         <v>17.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1340,10 +1340,10 @@
       <c r="U10" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="14" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1398,7 +1398,7 @@
       <c r="L11" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="13" t="n">
         <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1480,8 +1480,8 @@
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>191.7</v>
+      <c r="L12" s="13" t="n">
+        <v>19.17</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>22.1</v>
@@ -1580,7 +1580,7 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="13" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1598,8 +1598,8 @@
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>791.5</v>
+      <c r="W13" s="13" t="n">
+        <v>79.15000000000001</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>29.1</v>
@@ -1653,7 +1653,7 @@
       <c r="L14" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="13" t="n">
         <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1665,7 +1665,7 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="13" t="n">
         <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
@@ -1678,7 +1678,7 @@
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="13" t="n">
         <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1751,7 +1751,7 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="13" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1763,7 +1763,7 @@
       <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1815,13 +1815,13 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="14" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="14" t="n">
         <v>5.9</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="14" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1833,10 +1833,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="14" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="14" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1848,10 +1848,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="14" t="n">
         <v>9.5</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="14" t="n">
         <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1901,10 +1901,10 @@
         <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="14" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="14" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="8" t="n">
@@ -1916,10 +1916,10 @@
       <c r="P17" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="14" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1931,10 +1931,10 @@
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="14" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1986,10 +1986,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>1666.6</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="L18" s="13" t="n">
+        <v>166.66</v>
+      </c>
+      <c r="M18" s="13" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
@@ -2001,10 +2001,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="11" t="n">
         <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
@@ -2016,7 +2016,7 @@
       <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="11" t="n">
         <v>21</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2071,8 +2071,8 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>111.2</v>
+      <c r="L19" s="13" t="n">
+        <v>11.12</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>11</v>
@@ -2086,10 +2086,10 @@
       <c r="P19" s="8" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="11" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2101,7 +2101,7 @@
       <c r="U19" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2159,8 +2159,8 @@
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>211</v>
+      <c r="M20" s="13" t="n">
+        <v>21.1</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>13</v>
@@ -2171,10 +2171,10 @@
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2186,10 +2186,10 @@
       <c r="U20" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="13" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
@@ -2256,10 +2256,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2271,7 +2271,7 @@
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2341,10 +2341,10 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
@@ -2356,7 +2356,7 @@
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="11" t="n">
         <v>22.5</v>
       </c>
       <c r="W22" s="8" t="n">
@@ -2408,13 +2408,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="14" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2426,11 +2426,11 @@
       <c r="P23" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="R23" s="11" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>78.09999999999999</v>
@@ -2441,10 +2441,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="11" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="14" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2494,10 +2494,10 @@
         <v>16.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="14" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2509,10 +2509,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2524,10 +2524,10 @@
       <c r="U24" s="8" t="n">
         <v>177.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="14" t="n">
         <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2582,7 +2582,7 @@
       <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="13" t="n">
         <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
@@ -2594,7 +2594,7 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="13" t="n">
         <v>41.5</v>
       </c>
       <c r="R25" s="8" t="n">
@@ -2609,11 +2609,11 @@
       <c r="U25" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>216.9</v>
+      <c r="W25" s="13" t="n">
+        <v>21.69</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2664,8 +2664,8 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>109.4</v>
+      <c r="L26" s="13" t="n">
+        <v>10.94</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
@@ -2694,7 +2694,7 @@
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2767,8 +2767,8 @@
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>1618.2</v>
+      <c r="R27" s="13" t="n">
+        <v>161.82</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
@@ -2779,10 +2779,10 @@
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="13" t="n">
         <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2834,8 +2834,8 @@
       <c r="K28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L28" s="8" t="n">
-        <v>935.4</v>
+      <c r="L28" s="13" t="n">
+        <v>93.53999999999999</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
@@ -2864,7 +2864,7 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2937,8 +2937,8 @@
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="8" t="n">
-        <v>181.7</v>
+      <c r="R29" s="13" t="n">
+        <v>18.17</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>12</v>
@@ -2949,7 +2949,7 @@
       <c r="U29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -3001,13 +3001,13 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="14" t="n">
         <v>113.5</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="14" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="14" t="n">
         <v>56.7</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="14" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="14" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3032,10 +3032,10 @@
       <c r="U30" s="3" t="n">
         <v>55.9</v>
       </c>
-      <c r="V30" s="3" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="W30" s="3" t="n">
+      <c r="V30" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="W30" s="14" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3085,10 +3085,10 @@
         <v>39.1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="14" t="n">
         <v>11.5</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3100,10 +3100,10 @@
       <c r="P31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="14" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="14" t="n">
         <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3115,10 +3115,10 @@
       <c r="U31" s="3" t="n">
         <v>111.1</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3170,7 +3170,7 @@
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
@@ -3188,7 +3188,7 @@
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3255,7 +3255,7 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3273,7 +3273,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3340,7 +3340,7 @@
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="11" t="n">
         <v>12</v>
       </c>
       <c r="M34" s="8" t="n">
@@ -3358,7 +3358,7 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
@@ -3370,7 +3370,7 @@
       <c r="U34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3425,7 +3425,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="11" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3443,7 +3443,7 @@
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3510,7 +3510,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3528,7 +3528,7 @@
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3543,7 +3543,7 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="13" t="n">
         <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3590,13 +3590,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="14" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M37" s="3" t="n">
+      <c r="L37" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="M37" s="14" t="n">
         <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3608,11 +3608,11 @@
       <c r="P37" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="14" t="n">
         <v>185.9</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+      <c r="R37" s="11" t="n">
+        <v>88.8</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
@@ -3623,10 +3623,10 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="14" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="14" t="n">
         <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3676,10 +3676,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="14" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3691,10 +3691,10 @@
       <c r="P38" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="14" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3706,10 +3706,10 @@
       <c r="U38" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="14" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3756,13 +3756,13 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3792,7 +3792,7 @@
       <c r="V39" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
@@ -3839,7 +3839,7 @@
         <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
@@ -3857,7 +3857,7 @@
       <c r="P40" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="13" t="n">
         <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3875,8 +3875,8 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>181.5</v>
+      <c r="W40" s="11" t="n">
+        <v>18.15</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
@@ -3922,10 +3922,10 @@
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="13" t="n">
         <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3958,7 +3958,7 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4007,13 +4007,13 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4028,7 +4028,7 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
@@ -4043,7 +4043,7 @@
       <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4074,19 +4074,19 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="11" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4113,19 +4113,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="11" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4166,13 +4166,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="14" t="n">
         <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4184,10 +4184,10 @@
       <c r="P45" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="14" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="14" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4199,11 +4199,11 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="14" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="3" t="n">
-        <v>67.5</v>
+      <c r="W45" s="11" t="n">
+        <v>66.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>200.8</v>
@@ -4252,10 +4252,10 @@
         <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="14" t="n">
         <v>11181.9</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="14" t="n">
         <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4267,10 +4267,10 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="14" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="R46" s="14" t="n">
         <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4280,10 +4280,10 @@
         <v>54.1</v>
       </c>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="14" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -2007,14 +2007,14 @@
       <c r="R18" s="11" t="n">
         <v>17.3</v>
       </c>
-      <c r="S18" s="8" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>17.9</v>
+      <c r="S18" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>13.5</v>
       </c>
       <c r="V18" s="11" t="n">
         <v>21</v>
@@ -2092,14 +2092,14 @@
       <c r="R19" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>7.2</v>
+      <c r="S19" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="V19" s="11" t="n">
         <v>21.2</v>
@@ -2177,14 +2177,14 @@
       <c r="R20" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>22.4</v>
+      <c r="S20" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="V20" s="11" t="n">
         <v>22.2</v>
@@ -2262,14 +2262,14 @@
       <c r="R21" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>16.2</v>
+      <c r="S21" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="U21" s="11" t="n">
+        <v>11.9</v>
       </c>
       <c r="V21" s="11" t="n">
         <v>19.8</v>
@@ -2347,14 +2347,14 @@
       <c r="R22" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>14.8</v>
+      <c r="S22" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="V22" s="11" t="n">
         <v>22.5</v>
@@ -2515,14 +2515,14 @@
       <c r="R24" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>177.1</v>
+      <c r="S24" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="11" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="11" t="n">
         <v>21.3</v>
@@ -2612,16 +2612,16 @@
       <c r="V25" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="13" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="X25" s="8" t="n">
+      <c r="W25" s="11" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X25" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="3" t="n">
+      <c r="Y25" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="3" t="n">
+      <c r="Z25" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -3511,18 +3511,18 @@
         <v>0</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N36" s="11" t="n">
         <v>12.4</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
@@ -3594,7 +3594,7 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>66</v>
+        <v>65.7</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>6.4</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,22 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -778,22 +790,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>301.2</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="12" t="n">
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -802,52 +814,52 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>11.9</v>
+      <c r="N4" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>14.1</v>
+      <c r="S4" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>462.5</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="U4" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -865,20 +877,20 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>59.4</v>
+      <c r="G5" s="9" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -887,13 +899,13 @@
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="13" t="n">
-        <v>814.9399999999999</v>
+      <c r="M5" s="17" t="n">
+        <v>11.94</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -904,7 +916,7 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -916,21 +928,23 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="8" t="n">
+      <c r="U5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X5" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="9" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z5" s="3" t="n">
-        <v>469.5</v>
+      <c r="Z5" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -948,20 +962,20 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="E6" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -970,46 +984,46 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M6" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M6" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="N6" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="P6" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>24.6</v>
+      <c r="W6" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
@@ -1033,74 +1047,74 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>12.9</v>
+      <c r="H7" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>5</v>
+      <c r="M7" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>17.7</v>
+      <c r="S7" s="3" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1118,20 +1132,20 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="D8" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1142,43 +1156,43 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="13" t="n">
-        <v>271.94</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q8" s="12" t="n">
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
+      <c r="V8" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W8" s="17" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="X8" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1201,73 +1215,71 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>43927.4</v>
-      </c>
-      <c r="D9" s="11" t="n">
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>73.90000000000001</v>
+      <c r="G9" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12.6</v>
+        <v>140.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" s="14" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="M9" s="14" t="n">
-        <v>55.2</v>
+      <c r="K9" s="18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="M9" s="18" t="n">
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>766.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>684.8</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q9" s="14" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="18" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <v>85.3</v>
+      <c r="R9" s="18" t="n">
+        <v>185.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3801.5</v>
+        <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="14" t="n">
+      <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="14" t="n">
-        <v>8.4</v>
+      <c r="W9" s="18" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9414.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1286,18 +1298,18 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>8349.9</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1306,44 +1318,44 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>418.1</v>
+      <c r="J10" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q10" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="18" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="14" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S10" s="8" t="n">
+      <c r="R10" s="18" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="V10" s="14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="14" t="n">
+      <c r="W10" s="18" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1352,9 +1364,7 @@
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="Z10" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1371,17 +1381,17 @@
       <c r="C11" s="3" t="n">
         <v>509.3</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>16.6</v>
+      <c r="E11" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
@@ -1393,49 +1403,49 @@
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.2</v>
+        <v>26</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>1.2</v>
+        <v>11.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="12" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>17.9</v>
+      <c r="S11" s="12" t="n">
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>512</v>
-      </c>
-      <c r="U11" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U11" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="3" t="n">
+      <c r="X11" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1454,37 +1464,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="13" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>22.1</v>
+      <c r="L12" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1498,10 +1508,10 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="12" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
@@ -1510,17 +1520,17 @@
       <c r="U12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1541,38 +1551,38 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
@@ -1580,34 +1590,34 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="13" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="R13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>11.8</v>
+        <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>185.4</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="13" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y13" s="3" t="n">
+      <c r="W13" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X13" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="9" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1626,35 +1636,35 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G14" s="8" t="n">
+      <c r="D14" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>83</v>
+      <c r="I14" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>14.8</v>
@@ -1663,35 +1673,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>197</v>
+      </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="13" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="V14" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W14" s="12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="12" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1709,17 +1721,17 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15.6</v>
+      <c r="E15" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>50.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1733,8 +1745,8 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>27.4</v>
+      <c r="L15" s="17" t="n">
+        <v>77.40000000000001</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
@@ -1751,32 +1763,32 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
+      <c r="R15" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X15" s="3" t="n">
+      <c r="U15" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X15" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+      <c r="Z15" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1791,77 +1803,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2227.1</v>
-      </c>
-      <c r="D16" s="11" t="n">
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="G16" s="11" t="n">
+      <c r="E16" s="9" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="18" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="18" t="n">
         <v>5.9</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="18" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>57.1</v>
+        <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>399</v>
+        <v>489.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="Q16" s="18" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="14" t="n">
+      <c r="R16" s="9" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.9</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="V16" s="14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W16" s="14" t="n">
-        <v>801.7</v>
+        <v>603.9</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1879,16 +1889,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1897,54 +1907,54 @@
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>871.8</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="14" t="n">
+      <c r="J17" s="3" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L17" s="18" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="18" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="12" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q17" s="14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q17" s="18" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S17" s="8" t="n">
+      <c r="R17" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>42</v>
+        <v>362</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="V17" s="14" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="W17" s="18" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
       <c r="Z17" s="3" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1960,25 +1970,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>13.8</v>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1986,50 +1996,50 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="13" t="n">
-        <v>166.66</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="P18" s="3" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="P18" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S18" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T18" s="11" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="U18" s="11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V18" s="11" t="n">
+      <c r="R18" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U18" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="X18" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2045,19 +2055,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>17.4</v>
+      <c r="G19" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2071,10 +2081,10 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="13" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="M19" s="8" t="n">
+      <c r="L19" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2083,38 +2093,38 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U19" s="11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V19" s="11" t="n">
+      <c r="S19" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U19" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V19" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
+      <c r="W19" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X19" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y19" s="3" t="n">
+      <c r="Y19" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.6</v>
+      <c r="Z19" s="9" t="n">
+        <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2132,74 +2142,74 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>33.5</v>
+      <c r="I20" s="12" t="n">
+        <v>33.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="T20" s="11" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="U20" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="V20" s="11" t="n">
+      <c r="S20" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U20" s="12" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>299.7</v>
+      <c r="W20" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2217,74 +2227,74 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G21" s="11" t="n">
+      <c r="D21" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>15.9</v>
+      <c r="N21" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S21" s="11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="11" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="U21" s="11" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V21" s="11" t="n">
+      <c r="S21" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>20</v>
+      <c r="X21" s="12" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2300,40 +2310,40 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9489</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>989</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>18.7</v>
+      <c r="E22" s="17" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>11.2</v>
+        <v>8</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2341,29 +2351,29 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="T22" s="11" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U22" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V22" s="11" t="n">
+      <c r="S22" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>53.8</v>
+      <c r="X22" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
@@ -2385,55 +2395,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.3</v>
-      </c>
-      <c r="D23" s="11" t="n">
+        <v>2322.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="E23" s="18" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>75.40000000000001</v>
+      <c r="G23" s="3" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K23" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K23" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="14" t="n">
-        <v>61.8</v>
+      <c r="M23" s="18" t="n">
+        <v>161.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>2493</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q23" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="11" t="n">
-        <v>88.59999999999999</v>
+      <c r="R23" s="18" t="n">
+        <v>85</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2441,10 +2451,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="11" t="n">
+      <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="14" t="n">
+      <c r="W23" s="18" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2470,38 +2480,40 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2464.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F24" s="11" t="n">
+        <v>464.1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>57.1</v>
+      <c r="G24" s="9" t="n">
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L24" s="18" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="18" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>11.9</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2509,32 +2521,32 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="18" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T24" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U24" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V24" s="11" t="n">
+      <c r="S24" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X24" s="8" t="n">
+      <c r="W24" s="18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>58.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2553,75 +2565,75 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>488.9</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>13.6</v>
+      <c r="G25" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>49.7</v>
+        <v>4.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L25" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="M25" s="17" t="n">
         <v>2.9</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>19.4</v>
+      <c r="N25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>18</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="13" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="V25" s="11" t="n">
+      <c r="Q25" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S25" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="11" t="n">
+      <c r="Y25" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="11" t="n">
+      <c r="Z25" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2640,23 +2652,23 @@
       <c r="C26" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>23.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
@@ -2664,50 +2676,50 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="13" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="M26" s="8" t="n">
+      <c r="L26" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="V26" s="11" t="n">
+      <c r="S26" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X26" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+      <c r="X26" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y26" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="Z26" s="9" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2725,16 +2737,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2744,55 +2756,55 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="13" t="n">
-        <v>161.82</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V27" s="11" t="n">
+      <c r="R27" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>1.6</v>
+      <c r="W27" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X27" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2810,74 +2822,74 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <v>15.7</v>
+      <c r="G28" s="12" t="n">
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>93.53999999999999</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="N28" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P28" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V28" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="S28" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W28" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>817</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+      <c r="X28" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y28" s="9" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z28" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2893,19 +2905,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>18.1</v>
+      <c r="G29" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2919,50 +2931,50 @@
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="13" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T29" s="3" t="n">
+      <c r="R29" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="9" t="n">
         <v>47.8</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Y29" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v>112.9</v>
+      <c r="X29" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="Z29" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2978,49 +2990,51 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F30" s="11" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="3" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="L30" s="14" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="M30" s="14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="M30" s="18" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O30" s="3" t="n">
         <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="14" t="n">
+      <c r="Q30" s="9" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="14" t="n">
+      <c r="R30" s="9" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3030,22 +3044,22 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="V30" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="W30" s="14" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="W30" s="9" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>35</v>
+      <c r="X30" s="9" t="n">
+        <v>522</v>
+      </c>
+      <c r="Y30" s="9" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>506.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3061,74 +3075,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>432</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>452</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <v>58.4</v>
+      <c r="G31" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>39.1</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="14" t="n">
+      <c r="L31" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="M31" s="14" t="n">
+      <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q31" s="14" t="n">
+      <c r="N31" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="14" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S31" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>7</v>
+      <c r="W31" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X31" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y31" s="9" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z31" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3144,76 +3158,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5280.8</v>
-      </c>
-      <c r="D32" s="11" t="n">
+        <v>520</v>
+      </c>
+      <c r="D32" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>12.1</v>
+      <c r="L32" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R32" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>9.699999999999999</v>
+      <c r="S32" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>170</v>
-      </c>
+      <c r="X32" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>171.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3231,23 +3243,23 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>11.1</v>
+      <c r="G33" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3255,50 +3267,50 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.5</v>
+      <c r="L33" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R33" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.8</v>
+      <c r="S33" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W33" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="12" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3316,71 +3328,71 @@
       <c r="C34" s="3" t="n">
         <v>329.9</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>49.7</v>
+      <c r="H34" s="12" t="n">
+        <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>71.5</v>
+        <v>11.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="L34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.7</v>
+      <c r="N34" s="12" t="n">
+        <v>7.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>991</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3" t="n">
+      <c r="S34" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="12" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3401,16 +3413,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3425,47 +3437,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N35" s="3" t="n">
+      <c r="M35" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="O35" s="9" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="T35" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>16.8</v>
-      </c>
       <c r="Y35" s="3" t="n">
-        <v>683.5</v>
+        <v>68.3</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3486,73 +3498,75 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="11" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="E36" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M36" s="11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N36" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>99</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R36" s="11" t="n">
+      <c r="Q36" s="9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>17.9</v>
+      <c r="S36" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="13" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>11.3</v>
+      <c r="W36" s="9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="12" t="n">
+        <v>3.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3567,37 +3581,37 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2140.4</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="9" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="13" t="n">
-        <v>67.3</v>
+      <c r="G37" s="3" t="n">
+        <v>62.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>141.7</v>
+        <v>14.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L37" s="11" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="M37" s="14" t="n">
-        <v>6.4</v>
+      <c r="K37" s="18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L37" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>63.7</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
@@ -3605,38 +3619,36 @@
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="P37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q37" s="14" t="n">
-        <v>185.9</v>
-      </c>
-      <c r="R37" s="11" t="n">
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="9" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="R37" s="9" t="n">
         <v>88.8</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>2316.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="14" t="n">
+      <c r="V37" s="18" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="14" t="n">
-        <v>837.1</v>
+      <c r="W37" s="9" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.5</v>
+        <v>359.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.4</v>
+        <v>34.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3652,18 +3664,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3672,51 +3684,51 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>90.09999999999999</v>
+      <c r="J38" s="12" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="14" t="n">
+      <c r="M38" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q38" s="14" t="n">
+      <c r="O38" s="9" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V38" s="14" t="n">
+      <c r="S38" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V38" s="18" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="14" t="n">
+      <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3737,36 +3749,38 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F39" s="11" t="n">
+      <c r="D39" s="9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I39" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M39" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>1.7</v>
+      <c r="L39" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3774,35 +3788,33 @@
       <c r="P39" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>12.3</v>
+        <v>45.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>11.6</v>
+        <v>176</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3818,56 +3830,58 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>82</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.5</v>
+      <c r="S40" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.5</v>
+        <v>169.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3875,17 +3889,17 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="11" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X40" s="3" t="n">
+      <c r="W40" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y40" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="Y40" s="3" t="n">
-        <v>89</v>
-      </c>
       <c r="Z40" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1181.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3903,54 +3917,56 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>18.5</v>
+      <c r="D41" s="9" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>51</v>
+      </c>
       <c r="I41" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="13" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="M41" s="3" t="n">
+      <c r="L41" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
+      <c r="N41" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S41" s="3" t="n">
+      <c r="R41" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>423.5</v>
+        <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3958,17 +3974,17 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="11" t="n">
+      <c r="W41" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.8</v>
+        <v>111.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3984,39 +4000,39 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F42" s="11" t="n">
+      <c r="E42" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <v>135.2</v>
+      <c r="G42" s="17" t="n">
+        <v>12.6</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="11" t="n">
+      <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4025,30 +4041,26 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="13" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>12.7</v>
+      <c r="R42" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="U42" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="8" t="n">
+      <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="W42" s="16" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4067,26 +4079,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="11" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
-      <c r="R43" s="12" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
+      <c r="R43" s="16" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="12" t="inlineStr"/>
-      <c r="W43" s="11" t="inlineStr"/>
+      <c r="V43" s="16" t="inlineStr"/>
+      <c r="W43" s="16" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4106,26 +4118,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="K44" s="16" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
-      <c r="R44" s="12" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="16" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="inlineStr"/>
-      <c r="W44" s="11" t="inlineStr"/>
+      <c r="V44" s="16" t="inlineStr"/>
+      <c r="W44" s="16" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4143,76 +4155,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>1091.7</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F45" s="11" t="n">
+        <v>1981.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>27.9</v>
+      <c r="G45" s="17" t="n">
+        <v>10.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.9</v>
+        <v>16.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="14" t="n">
+      <c r="K45" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="14" t="n">
-        <v>22.9</v>
+      <c r="M45" s="9" t="n">
+        <v>42.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>31.6</v>
+        <v>5.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="14" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="R45" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="R45" s="18" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.9</v>
+        <v>216.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="14" t="n">
+      <c r="V45" s="18" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="11" t="n">
-        <v>66.5</v>
+      <c r="W45" s="18" t="n">
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>200.8</v>
+        <v>62.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1263</v>
+        <v>263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2331.8</v>
+        <v>35.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4228,37 +4240,39 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>417.8</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F46" s="11" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="9" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.6</v>
+        <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="14" t="n">
-        <v>11181.9</v>
-      </c>
-      <c r="M46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L46" s="18" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4267,30 +4281,32 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="14" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="14" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>11.6</v>
+      <c r="R46" s="18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>54.1</v>
       </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="14" t="n">
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V46" s="18" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="18" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>1.4</v>
+        <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1862.4</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1230,7 +1230,7 @@
       <c r="J9" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="16" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1808,7 +1808,7 @@
       <c r="J16" s="3" t="n">
         <v>139.8</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n">
         <v>59.9</v>
       </c>
@@ -1951,7 +1951,7 @@
       <c r="C18" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="12" t="n">
         <v>0.1</v>
       </c>
@@ -2138,7 +2138,7 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="14" t="n"/>
       <c r="L20" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="D22" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E22" s="13" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="F22" s="12" t="n">
         <v>81.7</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="J23" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2628,7 +2628,7 @@
       <c r="J26" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="K26" s="3" t="n"/>
+      <c r="K26" s="14" t="n"/>
       <c r="L26" s="3" t="n">
         <v>10.4</v>
       </c>
@@ -2962,7 +2962,7 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="16" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3549,7 +3549,7 @@
       <c r="J37" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="13" t="n"/>
       <c r="L37" s="3" t="n">
         <v>10.6</v>
       </c>
@@ -3798,7 +3798,7 @@
       <c r="J40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="14" t="n"/>
       <c r="L40" s="3" t="n">
         <v>12.7</v>
       </c>
@@ -4111,8 +4111,8 @@
       <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n">
         <v>0.1</v>
@@ -4194,7 +4194,7 @@
       <c r="J45" s="3" t="n">
         <v>221.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="16" t="n">
         <v>1.1</v>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -4250,8 +4250,8 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
       <c r="F46" s="16" t="n">
         <v>18.9</v>
       </c>
